--- a/Result/profitability/3528.xlsx
+++ b/Result/profitability/3528.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.29</v>
       </c>
       <c r="M2" t="n">
-        <v>1.145</v>
+        <v>1.365</v>
       </c>
       <c r="N2" t="n">
-        <v>11.75</v>
+        <v>11.66</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>1.17</v>
       </c>
       <c r="M3" t="n">
-        <v>1.17875</v>
+        <v>1.40625</v>
       </c>
       <c r="N3" t="n">
-        <v>12.445</v>
+        <v>12.72625</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2175</v>
+        <v>1.2975</v>
       </c>
       <c r="N4" t="n">
-        <v>13.2875</v>
+        <v>12.90125</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.85</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07125</v>
+        <v>1.82</v>
       </c>
       <c r="N5" t="n">
-        <v>12.95</v>
+        <v>13.3925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>98.3</v>
@@ -1137,10 +1137,10 @@
         <v>1.03</v>
       </c>
       <c r="M6" t="n">
-        <v>1.61625</v>
+        <v>1.75125</v>
       </c>
       <c r="N6" t="n">
-        <v>13.61125</v>
+        <v>13.6825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>1.625</v>
+        <v>1.70375</v>
       </c>
       <c r="N7" t="n">
-        <v>13.90625</v>
+        <v>13.725</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>1.38</v>
       </c>
       <c r="M8" t="n">
-        <v>1.54375</v>
+        <v>1.5225</v>
       </c>
       <c r="N8" t="n">
-        <v>14.1725</v>
+        <v>13.8125</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9445,6 +9445,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3528</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3201</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2849</v>
+      </c>
+      <c r="E72" t="n">
+        <v>352</v>
+      </c>
+      <c r="F72" t="n">
+        <v>11</v>
+      </c>
+      <c r="G72" t="n">
+        <v>220</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6.89%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J72" t="n">
+        <v>218</v>
+      </c>
+      <c r="K72" t="n">
+        <v>177</v>
+      </c>
+      <c r="L72" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.19125</v>
+      </c>
+      <c r="N72" t="n">
+        <v>11.2225</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>-0.1699999999999999</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-0.06007067137809186</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>-2.880000000000001</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>-0.2074927953890491</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-1.798798798798799</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.4745308310991958</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
